--- a/coronavirus_response_forms/034_gym_reopening_survey--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/034_gym_reopening_survey--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gym_reopening_survey_form</t>
+          <t>user_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gym_reopening_survey_form</t>
+          <t>1. What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,64 +543,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>last_week_visit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>2. Why did you not visit the gym last week?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what_do_you_miss_about_the_gym</t>
+          <t>feel_safe_again</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_do_you_miss_about_the_gym</t>
+          <t>3. What is the earliest date you would feel safe visiting the gym again?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>why_didnt_you_visit_the_gym_last_week</t>
+          <t>safety_measures</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>why_didnt_you_visit_the_gym_last_week</t>
+          <t>4. What safety measures do you expect the gym to have in place?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>what_will_it_take_for_you_to_feel_safe_to_visit_the_gym_again</t>
+          <t>visit_other_places</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_will_it_take_for_you_to_feel_safe_to_visit_the_gym_again</t>
+          <t>5. How often do you visit other places like restaurants?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +635,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place</t>
+          <t>visit_expectation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place</t>
+          <t>6. What do you expect from us when you visit the gym again?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options</t>
+          <t>communicate_with_us</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options</t>
+          <t>7. How do you prefer to communicate with us?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what_do_you_expect_from_us_when_you_visit_the_gym_again</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_do_you_expect_from_us_when_you_visit_the_gym_again</t>
+          <t>8. Do you have any other comments or concerns?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>are_you_planning_to_visit_the_gym_this_week</t>
+          <t>visit_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>are_you_planning_to_visit_the_gym_this_week</t>
+          <t>9. How often do you plan to visit the gym this week?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>do_you_have_any_other_comments</t>
+          <t>notification_preference</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>do_you_have_any_other_comments</t>
+          <t>10. How do you prefer to be notified?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>how_do_you_prefer_to_communicate_with_us</t>
+          <t>friends_family_member</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>how_do_you_prefer_to_communicate_with_us</t>
+          <t>11. Do you have any friends or family members that visit the gym?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>do_you_prefer_to_be_notified_by</t>
+          <t>gym_in_your_area</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>do_you_prefer_to_be_notified_by</t>
+          <t>12. Are there any other gyms in your area?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>are_there_any_other_gyms_in_your_area</t>
+          <t>other_gyms</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>are_there_any_other_gyms_in_your_area</t>
+          <t>Other Gyms</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>do_you_have_friends_and_family_member</t>
+          <t>visit_gym_again</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>do_you_have_friends_and_family_member</t>
+          <t>14. Are you planning to visit the gym again?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>how_ofen_do_you_visit_other_places_like_restaurants</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>how_ofen_do_you_visit_other_places_like_restaurants</t>
+          <t>15. How would you rate your last visit?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>how_many_hours</t>
+          <t>other_comments_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>how_many_hours</t>
+          <t>16. Do you have any other comments?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,228 +883,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>what_time</t>
+          <t>rating_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>what_time</t>
+          <t>17. How satisfied are you with our service?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>what_day</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>what_day</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>what_month</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>what_month</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>how_do_you_rate_your_last_visit</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>how_do_you_rate_your_last_visit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>why_didnt_you_visit_the_gym_last_week</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>why_didnt_you_visit_the_gym_last_week</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>what_will_prophets_expect_from_us</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>what_will_prophets_expect_from_us</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>what_do_you_expect_from_us_when_you_visit_the_gym_again</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what_do_you_expect_from_us_when_you_visit_the_gym_again</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>are_there_any_other_gyms_in_your_area</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>are_there_any_other_gyms_in_your_area</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>do_you_prefer_to_communicate_with_us</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>do_you_prefer_to_communicate_with_us</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>do_you_have_any_friends_or_family</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>do_you_have_any_friends_or_family</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,10 +914,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1149,7 +942,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options_choices</t>
+          <t>safety_measures_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1166,7 +959,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options_choices</t>
+          <t>safety_measures_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1183,7 +976,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options_choices</t>
+          <t>safety_measures_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1200,7 +993,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options_choices</t>
+          <t>safety_measures_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,7 +1010,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options_choices</t>
+          <t>safety_measures_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1234,714 +1027,255 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>what_safety_measures_do_you_expect_the_gym_to_have_in_place_options_choices</t>
+          <t>communicate_with_us_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>are_you_planning_to_visit_the_gym_this_week_choices</t>
+          <t>communicate_with_us_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>this_week</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>This week</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>are_you_planning_to_visit_the_gym_this_week_choices</t>
+          <t>communicate_with_us_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>next_week</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Next week</t>
+          <t>Message</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>are_you_planning_to_visit_the_gym_this_week_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>next_month</t>
+          <t>this_week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Next Month</t>
+          <t>This week</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>are_you_planning_to_visit_the_gym_this_week_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>next_week</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Next week</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_do_you_prefer_to_communicate_with_us_choices</t>
+          <t>visit_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>next_month</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Next month</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_do_you_prefer_to_communicate_with_us_choices</t>
+          <t>notification_preference_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>how_do_you_prefer_to_communicate_with_us_choices</t>
+          <t>notification_preference_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>how_do_you_prefer_to_communicate_with_us_choices</t>
+          <t>friends_family_member_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>In-person</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>do_you_prefer_to_be_notified_by_choices</t>
+          <t>friends_family_member_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>do_you_prefer_to_be_notified_by_choices</t>
+          <t>gym_in_your_area_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>are_there_any_other_gyms_in_your_area_choices</t>
+          <t>gym_in_your_area_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>are_there_any_other_gyms_in_your_area_choices</t>
+          <t>visit_gym_again_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>this_week</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>This week</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>do_you_have_friends_and_family_member_choices</t>
+          <t>visit_gym_again_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>next_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Next week</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>do_you_have_friends_and_family_member_choices</t>
+          <t>visit_gym_again_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>next_month</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>monday</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>wednesday</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>thursday</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>friday</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>saturday</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sunday</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>what_day_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>january</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>february</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>march</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>april</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>may</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>june</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>July</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>august</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>August</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>september</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>october</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>november</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>what_month_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>december</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>are_there_any_other_gyms_in_your_area_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>are_there_any_other_gyms_in_your_area_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>do_you_prefer_to_communicate_with_us_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>do_you_prefer_to_communicate_with_us_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>do_you_prefer_to_communicate_with_us_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>do_you_have_any_friends_or_family_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>do_you_have_any_friends_or_family_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>False</t>
+          <t>Next month</t>
         </is>
       </c>
     </row>
